--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/111.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/111.xlsx
@@ -426,13 +426,13 @@
         <v>-8.175959351451855</v>
       </c>
       <c r="E2">
-        <v>-16.56491093069535</v>
+        <v>-17.7101710641832</v>
       </c>
       <c r="F2">
-        <v>-1.372615702462525</v>
+        <v>-2.043104561962473</v>
       </c>
       <c r="G2">
-        <v>-9.620885033972565</v>
+        <v>-7.914787634366808</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.390557655857506</v>
       </c>
       <c r="E3">
-        <v>-17.4026423943223</v>
+        <v>-15.83775121691368</v>
       </c>
       <c r="F3">
-        <v>-1.290058121997318</v>
+        <v>-1.656329052819147</v>
       </c>
       <c r="G3">
-        <v>-10.60284636640291</v>
+        <v>-8.018940169106703</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.498516219411094</v>
       </c>
       <c r="E4">
-        <v>-17.71402932403773</v>
+        <v>-16.2522152719917</v>
       </c>
       <c r="F4">
-        <v>-1.579016694748467</v>
+        <v>-1.573196585376397</v>
       </c>
       <c r="G4">
-        <v>-9.952721532722327</v>
+        <v>-6.565598547446533</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.487248508642059</v>
       </c>
       <c r="E5">
-        <v>-18.87579121680953</v>
+        <v>-17.00266945606883</v>
       </c>
       <c r="F5">
-        <v>-1.4612592982361</v>
+        <v>-1.700872853169885</v>
       </c>
       <c r="G5">
-        <v>-10.15402447539426</v>
+        <v>-7.118257975925366</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.382626285008598</v>
       </c>
       <c r="E6">
-        <v>-18.97334360388277</v>
+        <v>-18.29305359608049</v>
       </c>
       <c r="F6">
-        <v>-1.710460377489887</v>
+        <v>-1.734586578096422</v>
       </c>
       <c r="G6">
-        <v>-11.50431933398007</v>
+        <v>-8.772052703873573</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.213886691050966</v>
       </c>
       <c r="E7">
-        <v>-19.94269969301667</v>
+        <v>-18.201256899471</v>
       </c>
       <c r="F7">
-        <v>-1.793869519645171</v>
+        <v>-1.483013882968421</v>
       </c>
       <c r="G7">
-        <v>-10.61336596272249</v>
+        <v>-7.632874921643997</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.016676279879029</v>
       </c>
       <c r="E8">
-        <v>-19.19701852054363</v>
+        <v>-18.58682023343207</v>
       </c>
       <c r="F8">
-        <v>-1.206098943886574</v>
+        <v>-1.611580645719918</v>
       </c>
       <c r="G8">
-        <v>-10.36454108820512</v>
+        <v>-8.173751483502864</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.813904871171882</v>
       </c>
       <c r="E9">
-        <v>-20.41918119962973</v>
+        <v>-20.48259794963315</v>
       </c>
       <c r="F9">
-        <v>-1.730326284543824</v>
+        <v>-1.53607992715916</v>
       </c>
       <c r="G9">
-        <v>-10.24618742655594</v>
+        <v>-9.794963681365784</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.62486691516619</v>
       </c>
       <c r="E10">
-        <v>-20.85284145602627</v>
+        <v>-19.57808507981508</v>
       </c>
       <c r="F10">
-        <v>-1.658011467014233</v>
+        <v>-0.7983044402646137</v>
       </c>
       <c r="G10">
-        <v>-9.788673579636329</v>
+        <v>-8.37497895807893</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.472445112124057</v>
       </c>
       <c r="E11">
-        <v>-21.0377662206035</v>
+        <v>-20.65127002099685</v>
       </c>
       <c r="F11">
-        <v>-1.192429225005577</v>
+        <v>-1.290386155488827</v>
       </c>
       <c r="G11">
-        <v>-9.962240356466276</v>
+        <v>-9.727951293457245</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.365420814863469</v>
       </c>
       <c r="E12">
-        <v>-22.21170970845593</v>
+        <v>-21.96080960606096</v>
       </c>
       <c r="F12">
-        <v>-1.463225842450346</v>
+        <v>-0.6360363780976214</v>
       </c>
       <c r="G12">
-        <v>-8.942292322042244</v>
+        <v>-7.709780192554263</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.296095015181921</v>
       </c>
       <c r="E13">
-        <v>-23.65289203292301</v>
+        <v>-24.18934864929367</v>
       </c>
       <c r="F13">
-        <v>-0.8112907560383016</v>
+        <v>-1.17170844279195</v>
       </c>
       <c r="G13">
-        <v>-9.520679808768682</v>
+        <v>-8.254889530224814</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.267410693504754</v>
       </c>
       <c r="E14">
-        <v>-25.54085360298685</v>
+        <v>-23.23529880230569</v>
       </c>
       <c r="F14">
-        <v>-0.6675425038956978</v>
+        <v>-0.3282581263222706</v>
       </c>
       <c r="G14">
-        <v>-8.998073088552804</v>
+        <v>-8.140158337177269</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.268435896217714</v>
       </c>
       <c r="E15">
-        <v>-24.6079517296147</v>
+        <v>-25.39896292690452</v>
       </c>
       <c r="F15">
-        <v>-0.2738178206102871</v>
+        <v>-0.2098098713959693</v>
       </c>
       <c r="G15">
-        <v>-9.741427270401886</v>
+        <v>-7.777589917301746</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.277275906269971</v>
       </c>
       <c r="E16">
-        <v>-25.63182158885294</v>
+        <v>-24.37614367363606</v>
       </c>
       <c r="F16">
-        <v>-0.1001464527763568</v>
+        <v>-0.1071254481449426</v>
       </c>
       <c r="G16">
-        <v>-8.75653580711896</v>
+        <v>-6.90415170672848</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.275897534946012</v>
       </c>
       <c r="E17">
-        <v>-27.06621573078252</v>
+        <v>-23.4404613172232</v>
       </c>
       <c r="F17">
-        <v>-0.005238742702811825</v>
+        <v>0.9760809024518029</v>
       </c>
       <c r="G17">
-        <v>-8.849975153467266</v>
+        <v>-7.395508072812206</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.24615821175501</v>
       </c>
       <c r="E18">
-        <v>-28.07546314744999</v>
+        <v>-26.66599825493263</v>
       </c>
       <c r="F18">
-        <v>0.6579579985502919</v>
+        <v>0.9375286835255139</v>
       </c>
       <c r="G18">
-        <v>-8.289867352048494</v>
+        <v>-6.242988843721929</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.165593206213453</v>
       </c>
       <c r="E19">
-        <v>-27.98477139849838</v>
+        <v>-27.66887410867131</v>
       </c>
       <c r="F19">
-        <v>0.486970541101432</v>
+        <v>0.8944071900053828</v>
       </c>
       <c r="G19">
-        <v>-7.895257803644994</v>
+        <v>-7.602723776734259</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.014954897551263</v>
       </c>
       <c r="E20">
-        <v>-29.57774137899156</v>
+        <v>-26.5145434417461</v>
       </c>
       <c r="F20">
-        <v>1.287787272451229</v>
+        <v>1.16462892047261</v>
       </c>
       <c r="G20">
-        <v>-7.0926480416539</v>
+        <v>-5.038662407429578</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.789403577418209</v>
       </c>
       <c r="E21">
-        <v>-29.98076650872621</v>
+        <v>-27.7390654557902</v>
       </c>
       <c r="F21">
-        <v>1.396069802610375</v>
+        <v>1.51751674753481</v>
       </c>
       <c r="G21">
-        <v>-8.587257586867207</v>
+        <v>-5.723771625376957</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.483750698134668</v>
       </c>
       <c r="E22">
-        <v>-31.14492396424806</v>
+        <v>-30.29185455915713</v>
       </c>
       <c r="F22">
-        <v>1.51455781917201</v>
+        <v>1.130032984262091</v>
       </c>
       <c r="G22">
-        <v>-6.8164544981092</v>
+        <v>-4.778914346340816</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.096509070219184</v>
       </c>
       <c r="E23">
-        <v>-30.59822620390906</v>
+        <v>-30.47260633493629</v>
       </c>
       <c r="F23">
-        <v>1.457938907190664</v>
+        <v>1.692194581763142</v>
       </c>
       <c r="G23">
-        <v>-7.41729210274536</v>
+        <v>-6.148922784055768</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.644051285038524</v>
       </c>
       <c r="E24">
-        <v>-31.99253882239676</v>
+        <v>-29.7206373763036</v>
       </c>
       <c r="F24">
-        <v>1.961307956645423</v>
+        <v>2.46348415704015</v>
       </c>
       <c r="G24">
-        <v>-7.632966795847661</v>
+        <v>-4.662483480525479</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.142779823595321</v>
       </c>
       <c r="E25">
-        <v>-31.17473038016655</v>
+        <v>-32.43528546188968</v>
       </c>
       <c r="F25">
-        <v>1.868890318984693</v>
+        <v>2.399520939665584</v>
       </c>
       <c r="G25">
-        <v>-7.372053901105296</v>
+        <v>-4.228486148522405</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.60948802876077</v>
       </c>
       <c r="E26">
-        <v>-33.54630580340554</v>
+        <v>-32.35785987754354</v>
       </c>
       <c r="F26">
-        <v>1.642994528241268</v>
+        <v>2.954808744458204</v>
       </c>
       <c r="G26">
-        <v>-6.397285006333258</v>
+        <v>-4.294448545531922</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.067551912381587</v>
       </c>
       <c r="E27">
-        <v>-32.43076830906703</v>
+        <v>-31.31557950722712</v>
       </c>
       <c r="F27">
-        <v>1.738053001182122</v>
+        <v>1.923554283895433</v>
       </c>
       <c r="G27">
-        <v>-6.92766494042346</v>
+        <v>-4.347751989765102</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.540430306528507</v>
       </c>
       <c r="E28">
-        <v>-31.92802618168349</v>
+        <v>-33.06350707555178</v>
       </c>
       <c r="F28">
-        <v>1.679548724992005</v>
+        <v>2.397635575456812</v>
       </c>
       <c r="G28">
-        <v>-7.046651877833604</v>
+        <v>-3.586236246584494</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.044453912031409</v>
       </c>
       <c r="E29">
-        <v>-32.20396648110388</v>
+        <v>-30.88084147401676</v>
       </c>
       <c r="F29">
-        <v>1.8873562851279</v>
+        <v>2.40480758043025</v>
       </c>
       <c r="G29">
-        <v>-5.985153734802322</v>
+        <v>-3.936857738762078</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.591009951865157</v>
       </c>
       <c r="E30">
-        <v>-30.86236756430247</v>
+        <v>-30.5703806172359</v>
       </c>
       <c r="F30">
-        <v>1.358460265788471</v>
+        <v>2.613117131212242</v>
       </c>
       <c r="G30">
-        <v>-6.357116292002535</v>
+        <v>-3.444021541755041</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.194034806687386</v>
       </c>
       <c r="E31">
-        <v>-32.63222200377226</v>
+        <v>-30.51881941218457</v>
       </c>
       <c r="F31">
-        <v>1.567185657006668</v>
+        <v>2.270245922784693</v>
       </c>
       <c r="G31">
-        <v>-5.760810054339968</v>
+        <v>-4.91698814956225</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.856193661690174</v>
       </c>
       <c r="E32">
-        <v>-32.00794242673385</v>
+        <v>-31.59031749679847</v>
       </c>
       <c r="F32">
-        <v>1.162249849291769</v>
+        <v>1.911670525134871</v>
       </c>
       <c r="G32">
-        <v>-5.457293778869773</v>
+        <v>-3.433570851088209</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.573061293223877</v>
       </c>
       <c r="E33">
-        <v>-31.34203938085394</v>
+        <v>-29.00830615066005</v>
       </c>
       <c r="F33">
-        <v>1.484942027787122</v>
+        <v>1.759613747942188</v>
       </c>
       <c r="G33">
-        <v>-5.763005191563237</v>
+        <v>-4.011039595778004</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.344143785711579</v>
       </c>
       <c r="E34">
-        <v>-31.35755619704122</v>
+        <v>-29.65088981963746</v>
       </c>
       <c r="F34">
-        <v>0.9061700071251358</v>
+        <v>1.398513486448633</v>
       </c>
       <c r="G34">
-        <v>-5.74980811845115</v>
+        <v>-4.3919598878355</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.162986611019945</v>
       </c>
       <c r="E35">
-        <v>-29.27792243612873</v>
+        <v>-28.46789164800669</v>
       </c>
       <c r="F35">
-        <v>1.085589416367092</v>
+        <v>1.98792008782776</v>
       </c>
       <c r="G35">
-        <v>-5.902191328893323</v>
+        <v>-4.316281793788467</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.019939710745712</v>
       </c>
       <c r="E36">
-        <v>-29.279262864435</v>
+        <v>-28.2048190074791</v>
       </c>
       <c r="F36">
-        <v>0.8131857661608913</v>
+        <v>1.23909749324948</v>
       </c>
       <c r="G36">
-        <v>-5.18584816292159</v>
+        <v>-4.351709142965792</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9081663681134212</v>
       </c>
       <c r="E37">
-        <v>-30.03619276634309</v>
+        <v>-30.05530292665546</v>
       </c>
       <c r="F37">
-        <v>0.9052554895124452</v>
+        <v>1.527882937213443</v>
       </c>
       <c r="G37">
-        <v>-4.731129916770622</v>
+        <v>-3.038583962205373</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8247393226377991</v>
       </c>
       <c r="E38">
-        <v>-28.18254797230937</v>
+        <v>-26.44154896921646</v>
       </c>
       <c r="F38">
-        <v>0.5291717184370528</v>
+        <v>1.091913173120063</v>
       </c>
       <c r="G38">
-        <v>-5.307597888884786</v>
+        <v>-2.169329309120398</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7667613292514949</v>
       </c>
       <c r="E39">
-        <v>-28.06908252757319</v>
+        <v>-28.75449423947814</v>
       </c>
       <c r="F39">
-        <v>0.7918420516603593</v>
+        <v>1.348344243065484</v>
       </c>
       <c r="G39">
-        <v>-5.397473828619536</v>
+        <v>-5.507398032082493</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.7317098692920586</v>
       </c>
       <c r="E40">
-        <v>-27.09579572300063</v>
+        <v>-27.98328153054986</v>
       </c>
       <c r="F40">
-        <v>0.7147458974818093</v>
+        <v>1.338420401579946</v>
       </c>
       <c r="G40">
-        <v>-5.237035219248927</v>
+        <v>-4.242972741707353</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7245378346642144</v>
       </c>
       <c r="E41">
-        <v>-28.19216645110167</v>
+        <v>-26.79195775945598</v>
       </c>
       <c r="F41">
-        <v>0.9020927827685566</v>
+        <v>0.7606523622101523</v>
       </c>
       <c r="G41">
-        <v>-5.505127426763358</v>
+        <v>-4.4912332461165</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7490274847812303</v>
       </c>
       <c r="E42">
-        <v>-27.18810866564699</v>
+        <v>-25.03665330697284</v>
       </c>
       <c r="F42">
-        <v>0.5826378640833442</v>
+        <v>1.1049732135926</v>
       </c>
       <c r="G42">
-        <v>-6.035179238697617</v>
+        <v>-3.934905411934208</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8078877908420892</v>
       </c>
       <c r="E43">
-        <v>-24.98623327737144</v>
+        <v>-24.69526070848259</v>
       </c>
       <c r="F43">
-        <v>0.5376276928848301</v>
+        <v>1.289212064384044</v>
       </c>
       <c r="G43">
-        <v>-6.062423221305687</v>
+        <v>-4.441916486078046</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.9053032435088326</v>
       </c>
       <c r="E44">
-        <v>-25.52648475496052</v>
+        <v>-23.21299153934391</v>
       </c>
       <c r="F44">
-        <v>0.6203749694852784</v>
+        <v>1.333145357958919</v>
       </c>
       <c r="G44">
-        <v>-5.897016842494078</v>
+        <v>-5.647502911449224</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.04588217829807</v>
       </c>
       <c r="E45">
-        <v>-24.71352857262953</v>
+        <v>-23.91347401274639</v>
       </c>
       <c r="F45">
-        <v>0.5102153587913889</v>
+        <v>1.054176067718129</v>
       </c>
       <c r="G45">
-        <v>-5.85037755924813</v>
+        <v>-4.473235745862945</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.230191189095477</v>
       </c>
       <c r="E46">
-        <v>-23.67857753749452</v>
+        <v>-20.85340751527723</v>
       </c>
       <c r="F46">
-        <v>0.7696434620001381</v>
+        <v>1.473547005794212</v>
       </c>
       <c r="G46">
-        <v>-5.901229930976405</v>
+        <v>-4.568040080379982</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.453879582777925</v>
       </c>
       <c r="E47">
-        <v>-23.48163420290093</v>
+        <v>-20.65496525578711</v>
       </c>
       <c r="F47">
-        <v>0.5137624280101765</v>
+        <v>2.034656576693708</v>
       </c>
       <c r="G47">
-        <v>-4.449020330754244</v>
+        <v>-3.905065983072618</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.715750439373619</v>
       </c>
       <c r="E48">
-        <v>-21.34613718662982</v>
+        <v>-21.15579636713942</v>
       </c>
       <c r="F48">
-        <v>1.237250233941237</v>
+        <v>1.750612707743369</v>
       </c>
       <c r="G48">
-        <v>-5.501491833275493</v>
+        <v>-3.876197795792623</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.010759353860388</v>
       </c>
       <c r="E49">
-        <v>-22.55607298589522</v>
+        <v>-20.30253676614016</v>
       </c>
       <c r="F49">
-        <v>0.980902000736096</v>
+        <v>1.358519908241473</v>
       </c>
       <c r="G49">
-        <v>-5.505107739434001</v>
+        <v>-4.610292370400952</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.328583580037783</v>
       </c>
       <c r="E50">
-        <v>-21.34643153744032</v>
+        <v>-19.44613893265359</v>
       </c>
       <c r="F50">
-        <v>0.6741161331092991</v>
+        <v>1.641702275092901</v>
       </c>
       <c r="G50">
-        <v>-5.98381171518451</v>
+        <v>-6.476631506083749</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.663166924597613</v>
       </c>
       <c r="E51">
-        <v>-19.96221741598973</v>
+        <v>-18.72625194812824</v>
       </c>
       <c r="F51">
-        <v>1.203676503105773</v>
+        <v>1.5243491218731</v>
       </c>
       <c r="G51">
-        <v>-6.191201323849213</v>
+        <v>-3.714554978109698</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.008605503581157</v>
       </c>
       <c r="E52">
-        <v>-20.13429037133319</v>
+        <v>-17.77103375484629</v>
       </c>
       <c r="F52">
-        <v>1.276900868043638</v>
+        <v>0.887448903821867</v>
       </c>
       <c r="G52">
-        <v>-5.928221259524397</v>
+        <v>-4.124628923722861</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.356296538662455</v>
       </c>
       <c r="E53">
-        <v>-18.76523305238627</v>
+        <v>-17.51706787554812</v>
       </c>
       <c r="F53">
-        <v>0.7908331001637494</v>
+        <v>1.787337548179082</v>
       </c>
       <c r="G53">
-        <v>-5.569334370238572</v>
+        <v>-5.365688635373195</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.697905737895298</v>
       </c>
       <c r="E54">
-        <v>-18.98740451567658</v>
+        <v>-17.11120792108467</v>
       </c>
       <c r="F54">
-        <v>0.7978725663527396</v>
+        <v>1.385262921473452</v>
       </c>
       <c r="G54">
-        <v>-6.575609554424399</v>
+        <v>-4.611677045899038</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.030829548702889</v>
       </c>
       <c r="E55">
-        <v>-17.75226323008449</v>
+        <v>-16.42115905179586</v>
       </c>
       <c r="F55">
-        <v>0.4613955259074001</v>
+        <v>1.373780092535846</v>
       </c>
       <c r="G55">
-        <v>-6.367881979939073</v>
+        <v>-4.549419148030133</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.350756206490034</v>
       </c>
       <c r="E56">
-        <v>-17.38347789232184</v>
+        <v>-16.10595009001796</v>
       </c>
       <c r="F56">
-        <v>0.932735749732916</v>
+        <v>1.352595424576651</v>
       </c>
       <c r="G56">
-        <v>-6.807838010294099</v>
+        <v>-4.361408433895511</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.64898342791296</v>
       </c>
       <c r="E57">
-        <v>-16.74436982714532</v>
+        <v>-16.5789944848592</v>
       </c>
       <c r="F57">
-        <v>0.6427748524243798</v>
+        <v>0.9534233972504308</v>
       </c>
       <c r="G57">
-        <v>-7.072091188583979</v>
+        <v>-4.23962589571672</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.926978849909438</v>
       </c>
       <c r="E58">
-        <v>-15.78567829429948</v>
+        <v>-14.27549561137752</v>
       </c>
       <c r="F58">
-        <v>0.4212395876892913</v>
+        <v>1.431137908240489</v>
       </c>
       <c r="G58">
-        <v>-6.415266100479014</v>
+        <v>-7.154144696121013</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.183632132654923</v>
       </c>
       <c r="E59">
-        <v>-15.91444545270759</v>
+        <v>-14.48113814453984</v>
       </c>
       <c r="F59">
-        <v>0.4589907753370731</v>
+        <v>1.753752220199979</v>
       </c>
       <c r="G59">
-        <v>-6.806082556759796</v>
+        <v>-5.4818307536913</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.413181124110655</v>
       </c>
       <c r="E60">
-        <v>-14.2231147525308</v>
+        <v>-13.4353640565265</v>
       </c>
       <c r="F60">
-        <v>0.1324500018883136</v>
+        <v>1.017421406055915</v>
       </c>
       <c r="G60">
-        <v>-7.094436307403797</v>
+        <v>-5.471655685635462</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.615058230750254</v>
       </c>
       <c r="E61">
-        <v>-14.89577881010416</v>
+        <v>-13.94018928195358</v>
       </c>
       <c r="F61">
-        <v>-0.304503862679592</v>
+        <v>0.5495039963387667</v>
       </c>
       <c r="G61">
-        <v>-7.011086717350783</v>
+        <v>-5.117352662868181</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.788972142163531</v>
       </c>
       <c r="E62">
-        <v>-13.68453881032456</v>
+        <v>-12.62848508631381</v>
       </c>
       <c r="F62">
-        <v>0.1835039416576527</v>
+        <v>0.8329754634137715</v>
       </c>
       <c r="G62">
-        <v>-6.78987004103458</v>
+        <v>-5.86881802441221</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.930665686946815</v>
       </c>
       <c r="E63">
-        <v>-13.03413220249889</v>
+        <v>-11.7996384886899</v>
       </c>
       <c r="F63">
-        <v>0.3131219026433026</v>
+        <v>0.9915912537018209</v>
       </c>
       <c r="G63">
-        <v>-6.890183546549923</v>
+        <v>-7.16574381433365</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.035945860914148</v>
       </c>
       <c r="E64">
-        <v>-13.16990491019687</v>
+        <v>-12.06958082428713</v>
       </c>
       <c r="F64">
-        <v>-0.4795370665237247</v>
+        <v>0.9211800244638628</v>
       </c>
       <c r="G64">
-        <v>-7.144465092520651</v>
+        <v>-6.842510678512751</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.106848176892441</v>
       </c>
       <c r="E65">
-        <v>-12.37070170342717</v>
+        <v>-10.47547193258102</v>
       </c>
       <c r="F65">
-        <v>-0.5971942305803525</v>
+        <v>0.5188659995788242</v>
       </c>
       <c r="G65">
-        <v>-7.345072416221982</v>
+        <v>-6.841168658894938</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.141806885281306</v>
       </c>
       <c r="E66">
-        <v>-12.43130174259781</v>
+        <v>-10.42547305106233</v>
       </c>
       <c r="F66">
-        <v>-0.2920733814331826</v>
+        <v>0.6233239574392446</v>
       </c>
       <c r="G66">
-        <v>-7.151070191519813</v>
+        <v>-5.103046536869003</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.135088348363499</v>
       </c>
       <c r="E67">
-        <v>-12.61402114033331</v>
+        <v>-10.35893165399362</v>
       </c>
       <c r="F67">
-        <v>-0.5759565471073788</v>
+        <v>0.4224274665449058</v>
       </c>
       <c r="G67">
-        <v>-7.730130328665939</v>
+        <v>-6.932882082702977</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.091805160143736</v>
       </c>
       <c r="E68">
-        <v>-11.6338555837431</v>
+        <v>-10.53541987149456</v>
       </c>
       <c r="F68">
-        <v>-0.6558293888201128</v>
+        <v>-0.299475672544599</v>
       </c>
       <c r="G68">
-        <v>-7.707575211666316</v>
+        <v>-6.467358773956758</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.01296249347799</v>
       </c>
       <c r="E69">
-        <v>-11.30093576012119</v>
+        <v>-10.37263481634083</v>
       </c>
       <c r="F69">
-        <v>-1.043022395134449</v>
+        <v>-0.01973931408881717</v>
       </c>
       <c r="G69">
-        <v>-7.375781368796825</v>
+        <v>-5.665700566217904</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.896190589510332</v>
       </c>
       <c r="E70">
-        <v>-12.77732244152391</v>
+        <v>-11.01289311391531</v>
       </c>
       <c r="F70">
-        <v>-1.224102681019018</v>
+        <v>-0.4259582629106528</v>
       </c>
       <c r="G70">
-        <v>-7.099952040845224</v>
+        <v>-5.136482184559744</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.746412868065073</v>
       </c>
       <c r="E71">
-        <v>-11.98511572709606</v>
+        <v>-11.24026326536643</v>
       </c>
       <c r="F71">
-        <v>-1.806600698258797</v>
+        <v>-0.3848422468726992</v>
       </c>
       <c r="G71">
-        <v>-5.988201989631047</v>
+        <v>-5.392200905573509</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.567743711281815</v>
       </c>
       <c r="E72">
-        <v>-11.99172277067325</v>
+        <v>-10.57091405076668</v>
       </c>
       <c r="F72">
-        <v>-1.432568793240139</v>
+        <v>-0.9736731329068803</v>
       </c>
       <c r="G72">
-        <v>-6.057402952319736</v>
+        <v>-6.467394867393913</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.360027157831851</v>
       </c>
       <c r="E73">
-        <v>-12.7343381662431</v>
+        <v>-10.50203596111001</v>
       </c>
       <c r="F73">
-        <v>-1.941639495528367</v>
+        <v>-1.191183360431766</v>
       </c>
       <c r="G73">
-        <v>-5.965495936439689</v>
+        <v>-5.55575339420403</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.124542657973897</v>
       </c>
       <c r="E74">
-        <v>-11.40139995598136</v>
+        <v>-11.35121540702836</v>
       </c>
       <c r="F74">
-        <v>-1.398109537651083</v>
+        <v>-1.267292100666179</v>
       </c>
       <c r="G74">
-        <v>-4.832693567700114</v>
+        <v>-5.980569868283778</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.866655853854892</v>
       </c>
       <c r="E75">
-        <v>-11.23317620354442</v>
+        <v>-11.13850845441407</v>
       </c>
       <c r="F75">
-        <v>-1.897406332953679</v>
+        <v>-1.298567940326277</v>
       </c>
       <c r="G75">
-        <v>-5.164539910114556</v>
+        <v>-5.355552941976071</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.586628912769374</v>
       </c>
       <c r="E76">
-        <v>-12.16282663257907</v>
+        <v>-10.95468863749472</v>
       </c>
       <c r="F76">
-        <v>-2.142440724171384</v>
+        <v>-2.000732740941875</v>
       </c>
       <c r="G76">
-        <v>-5.289193517157861</v>
+        <v>-4.10891187245312</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.281851672268743</v>
       </c>
       <c r="E77">
-        <v>-13.06351294186066</v>
+        <v>-11.18981153644697</v>
       </c>
       <c r="F77">
-        <v>-2.194385987266135</v>
+        <v>-1.92621529448824</v>
       </c>
       <c r="G77">
-        <v>-4.633195296885876</v>
+        <v>-4.247356453710772</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.958204169969598</v>
       </c>
       <c r="E78">
-        <v>-13.05895276853493</v>
+        <v>-11.32941986162944</v>
       </c>
       <c r="F78">
-        <v>-2.056434650208323</v>
+        <v>-1.563036659181061</v>
       </c>
       <c r="G78">
-        <v>-4.352404761936394</v>
+        <v>-2.960323546791058</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.615491601576362</v>
       </c>
       <c r="E79">
-        <v>-13.49700564471891</v>
+        <v>-13.192420482963</v>
       </c>
       <c r="F79">
-        <v>-2.634268130602937</v>
+        <v>-1.811876570247227</v>
       </c>
       <c r="G79">
-        <v>-3.43598911137752</v>
+        <v>-3.21055934657899</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.251482713033208</v>
       </c>
       <c r="E80">
-        <v>-13.96221125105288</v>
+        <v>-13.08479676969671</v>
       </c>
       <c r="F80">
-        <v>-2.12248121160093</v>
+        <v>-1.751235934525289</v>
       </c>
       <c r="G80">
-        <v>-3.167650812246131</v>
+        <v>-3.824649805093747</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.870580271424205</v>
       </c>
       <c r="E81">
-        <v>-13.84731480853027</v>
+        <v>-12.36231949803897</v>
       </c>
       <c r="F81">
-        <v>-2.763959816287436</v>
+        <v>-1.739487199651384</v>
       </c>
       <c r="G81">
-        <v>-2.404081024369311</v>
+        <v>-2.024460096049355</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.47504426558943</v>
       </c>
       <c r="E82">
-        <v>-14.38737156173702</v>
+        <v>-13.74889295444756</v>
       </c>
       <c r="F82">
-        <v>-3.256628015632831</v>
+        <v>-2.807395261053228</v>
       </c>
       <c r="G82">
-        <v>-3.488258970819474</v>
+        <v>-1.051302281063003</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.065012634062954</v>
       </c>
       <c r="E83">
-        <v>-15.0111054576575</v>
+        <v>-14.14073728185727</v>
       </c>
       <c r="F83">
-        <v>-2.829649351329437</v>
+        <v>-1.916632740372656</v>
       </c>
       <c r="G83">
-        <v>-3.47800187222465</v>
+        <v>-1.39977785434071</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.644822712334274</v>
       </c>
       <c r="E84">
-        <v>-16.73767221408797</v>
+        <v>-15.84139211001585</v>
       </c>
       <c r="F84">
-        <v>-3.032673918081568</v>
+        <v>-1.982819295856336</v>
       </c>
       <c r="G84">
-        <v>-1.699100728657935</v>
+        <v>-0.4593567868529384</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.220285311974101</v>
       </c>
       <c r="E85">
-        <v>-17.30107325080427</v>
+        <v>-15.23725292112655</v>
       </c>
       <c r="F85">
-        <v>-2.905477275014301</v>
+        <v>-2.341830414760031</v>
       </c>
       <c r="G85">
-        <v>-1.991815222754439</v>
+        <v>-0.09258184093820811</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7950667257889477</v>
       </c>
       <c r="E86">
-        <v>-17.75879781807756</v>
+        <v>-16.62128137514283</v>
       </c>
       <c r="F86">
-        <v>-3.484564903656754</v>
+        <v>-2.655042756697746</v>
       </c>
       <c r="G86">
-        <v>-1.498096377147911</v>
+        <v>-1.068079166896444</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3735473581433125</v>
       </c>
       <c r="E87">
-        <v>-19.80001200550898</v>
+        <v>-19.52707182011867</v>
       </c>
       <c r="F87">
-        <v>-3.49866040338279</v>
+        <v>-2.947346277021399</v>
       </c>
       <c r="G87">
-        <v>-2.274607302855182</v>
+        <v>-1.854112197569223</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.03482999179513531</v>
       </c>
       <c r="E88">
-        <v>-19.94347859054599</v>
+        <v>-20.24551874990959</v>
       </c>
       <c r="F88">
-        <v>-3.583053646012601</v>
+        <v>-3.802861764712853</v>
       </c>
       <c r="G88">
-        <v>-2.248193469301652</v>
+        <v>-1.674179850913953</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.4246099925694412</v>
       </c>
       <c r="E89">
-        <v>-21.17893234084461</v>
+        <v>-20.28703579961191</v>
       </c>
       <c r="F89">
-        <v>-3.948833354964571</v>
+        <v>-3.071584820093269</v>
       </c>
       <c r="G89">
-        <v>-1.560180370274165</v>
+        <v>-0.3847483710342845</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7900383551799269</v>
       </c>
       <c r="E90">
-        <v>-23.28661546976061</v>
+        <v>-23.68426530084815</v>
       </c>
       <c r="F90">
-        <v>-4.703797465467207</v>
+        <v>-2.782187212618636</v>
       </c>
       <c r="G90">
-        <v>-1.819055626428115</v>
+        <v>-1.02502297759341</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.12168654546087</v>
       </c>
       <c r="E91">
-        <v>-24.38568516837022</v>
+        <v>-22.82998679319717</v>
       </c>
       <c r="F91">
-        <v>-4.513940626949976</v>
+        <v>-3.541990645488427</v>
       </c>
       <c r="G91">
-        <v>-1.670301447030689</v>
+        <v>0.1257375167410055</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.412571076106481</v>
       </c>
       <c r="E92">
-        <v>-26.45873452807557</v>
+        <v>-26.31476981089772</v>
       </c>
       <c r="F92">
-        <v>-4.619385998754534</v>
+        <v>-4.553485230024819</v>
       </c>
       <c r="G92">
-        <v>-1.987677602367979</v>
+        <v>1.487277121611031</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.657175009985694</v>
       </c>
       <c r="E93">
-        <v>-26.9733367288852</v>
+        <v>-27.90409663405173</v>
       </c>
       <c r="F93">
-        <v>-4.840282592222064</v>
+        <v>-4.190336415944142</v>
       </c>
       <c r="G93">
-        <v>-1.567697648866853</v>
+        <v>0.1130851264077867</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.849165652417774</v>
       </c>
       <c r="E94">
-        <v>-28.66488026734035</v>
+        <v>-28.76718302364763</v>
       </c>
       <c r="F94">
-        <v>-5.287466794214544</v>
+        <v>-5.14912446774261</v>
       </c>
       <c r="G94">
-        <v>-2.605249436957307</v>
+        <v>-1.099395145459784</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.98555753423878</v>
       </c>
       <c r="E95">
-        <v>-31.0108086780369</v>
+        <v>-30.23537769557047</v>
       </c>
       <c r="F95">
-        <v>-5.611587078112323</v>
+        <v>-4.801709664110705</v>
       </c>
       <c r="G95">
-        <v>-2.326850912524661</v>
+        <v>-2.185492606522223</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.063456821684038</v>
       </c>
       <c r="E96">
-        <v>-33.2597666105702</v>
+        <v>-31.30360848618784</v>
       </c>
       <c r="F96">
-        <v>-5.501467229053768</v>
+        <v>-5.087638897269816</v>
       </c>
       <c r="G96">
-        <v>-2.590785812323275</v>
+        <v>-1.279078119276536</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.086383692448439</v>
       </c>
       <c r="E97">
-        <v>-34.40474597866957</v>
+        <v>-34.47738949446362</v>
       </c>
       <c r="F97">
-        <v>-5.59707242448047</v>
+        <v>-5.294024150575105</v>
       </c>
       <c r="G97">
-        <v>-3.376096974252976</v>
+        <v>-2.150708376770549</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.04946112602236</v>
       </c>
       <c r="E98">
-        <v>-37.30081152571395</v>
+        <v>-33.88479791429388</v>
       </c>
       <c r="F98">
-        <v>-5.581741000589457</v>
+        <v>-5.645197257113511</v>
       </c>
       <c r="G98">
-        <v>-4.173679904815</v>
+        <v>-2.438566662959075</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.967415337475042</v>
       </c>
       <c r="E99">
-        <v>-39.2519543651328</v>
+        <v>-37.5725380800702</v>
       </c>
       <c r="F99">
-        <v>-5.742936326969824</v>
+        <v>-5.975119426300497</v>
       </c>
       <c r="G99">
-        <v>-4.328471531881805</v>
+        <v>-2.547490093846402</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.829865573363069</v>
       </c>
       <c r="E100">
-        <v>-40.97924114893049</v>
+        <v>-39.81767398054102</v>
       </c>
       <c r="F100">
-        <v>-6.145619803716511</v>
+        <v>-6.147036311975298</v>
       </c>
       <c r="G100">
-        <v>-4.827663455049485</v>
+        <v>-3.222578461151236</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.667715139167509</v>
       </c>
       <c r="E101">
-        <v>-43.29632091596118</v>
+        <v>-42.15340200353529</v>
       </c>
       <c r="F101">
-        <v>-6.509113218636754</v>
+        <v>-6.219653483606911</v>
       </c>
       <c r="G101">
-        <v>-4.679365365448822</v>
+        <v>-2.825422684817607</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.447412825630273</v>
       </c>
       <c r="E102">
-        <v>-43.92111221056245</v>
+        <v>-43.68420282861418</v>
       </c>
       <c r="F102">
-        <v>-6.108832835725588</v>
+        <v>-5.650533599922345</v>
       </c>
       <c r="G102">
-        <v>-5.462133580669954</v>
+        <v>-3.776392879618993</v>
       </c>
     </row>
   </sheetData>
